--- a/Resultados/RGAA/ldf_rgaa_RC daños a cosas.xlsx
+++ b/Resultados/RGAA/ldf_rgaa_RC daños a cosas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\Python Script\Github\IBNR-NIIF-17\Resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Python_script\Github\IBNR-NIIF-17\Resultados\RGAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D09791-B0CF-44F5-89F4-5ACBC4F90DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44DBB93-3D3B-416E-9B82-7440DFFC7836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -66,6 +66,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -206,12 +209,12 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,88 +517,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C6:I20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="D8:R20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="5.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="8" t="s">
+    <row r="8" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="1" t="s">
+    <row r="9" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="L9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="5">
-        <v>1.1994341194934199</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.0377940660686511</v>
-      </c>
-      <c r="F7" s="6">
-        <v>1.016469564081258</v>
-      </c>
-      <c r="G7" s="6">
-        <v>1.013984214594744</v>
-      </c>
-      <c r="H7" s="6">
-        <v>1.0096278022949221</v>
-      </c>
-      <c r="I7" s="7">
+      <c r="M9" s="4">
+        <v>1.1944551199766771</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1.03362632206403</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.014597944623685</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1.0111667797381609</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>1.007633508551379</v>
+      </c>
+      <c r="R9" s="6">
         <v>1.05</v>
       </c>
     </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="1" t="s">
+    <row r="10" spans="4:18" x14ac:dyDescent="0.25">
+      <c r="L10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3">
-        <f t="shared" ref="D8:G8" si="0">E8*D7</f>
-        <v>1.360077811557945</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="M10" s="7">
+        <f t="shared" ref="M10:P10" si="0">N10*M9</f>
+        <v>1.3401150008245963</v>
+      </c>
+      <c r="N10" s="7">
         <f t="shared" si="0"/>
-        <v>1.1339329017356725</v>
-      </c>
-      <c r="F8" s="3">
+        <v>1.1219467173038393</v>
+      </c>
+      <c r="O10" s="7">
         <f t="shared" si="0"/>
-        <v>1.0926376810297369</v>
-      </c>
-      <c r="G8" s="3">
+        <v>1.0854471227700973</v>
+      </c>
+      <c r="P10" s="7">
         <f t="shared" si="0"/>
-        <v>1.0749339868501857</v>
-      </c>
-      <c r="H8" s="3">
-        <f>I8*H7</f>
-        <v>1.0601091924096682</v>
-      </c>
-      <c r="I8" s="4">
-        <f>I7</f>
+        <v>1.0698298064980707</v>
+      </c>
+      <c r="Q10" s="7">
+        <f>R10*Q9</f>
+        <v>1.058015183978948</v>
+      </c>
+      <c r="R10" s="8">
+        <f>R9</f>
         <v>1.05</v>
       </c>
     </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D12">
         <v>1.360077811557945</v>
       </c>
@@ -615,32 +622,32 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D15">
         <v>1.360077811557945</v>
       </c>
     </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D16">
         <v>1.1339329017356725</v>
       </c>
     </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D17">
         <v>1.0926376810297369</v>
       </c>
     </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D18">
         <v>1.0749339868501857</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19">
         <v>1.0601091924096682</v>
       </c>
     </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D20">
         <v>1.05</v>
       </c>
